--- a/data/trans_camb/IP1008-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1008-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,0</t>
+          <t>-2,84; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,0</t>
+          <t>-2,6; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 0,0</t>
+          <t>-4,34; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 0,0</t>
+          <t>-4,69; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; -0,26</t>
+          <t>-2,6; -0,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; -0,26</t>
+          <t>-2,54; -0,26</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,56</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,86</t>
+          <t>0,0; 5,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,31; 2,62</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,0</t>
+          <t>-3,44; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,0</t>
+          <t>-3,55; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,0</t>
+          <t>-1,63; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,0</t>
+          <t>-2,01; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,67</t>
+          <t>-1,6; 0,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,78</t>
+          <t>-1,01; 1,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,54</t>
+          <t>-0,71; 0,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,3</t>
+          <t>-0,36; 1,29</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,86</t>
+          <t>-1,49; 1,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,02</t>
+          <t>-1,27; 2,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,49</t>
+          <t>-2,25; 1,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,0</t>
+          <t>-3,86; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,31</t>
+          <t>-1,33; 1,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,9</t>
+          <t>-1,78; 0,75</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1416,27 +1416,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,14</t>
+          <t>0,0; 5,08</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 5,23</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,71</t>
+          <t>0,0; 5,11</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 3,08</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 3,46</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,75</t>
+          <t>-0,44; 0,73</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,3</t>
+          <t>-0,11; 1,39</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,53</t>
+          <t>-0,61; 0,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,24</t>
+          <t>-0,8; 0,33</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,5</t>
+          <t>-0,39; 0,42</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,57</t>
+          <t>-0,32; 0,6</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,13; 576,69</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-45,73; 927,08</t>
+          <t>-39,05; 995,23</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-84,29; 311,74</t>
+          <t>-85,56; 353,67</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 178,06</t>
+          <t>-100,0; 352,9</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-59,02; 255,19</t>
+          <t>-65,76; 167,31</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-50,5; 235,08</t>
+          <t>-53,15; 247,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1008-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1008-Clase-trans_camb.xlsx
@@ -631,22 +631,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,0</t>
+          <t>-3,05; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,0</t>
+          <t>-3,22; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,0</t>
+          <t>-4,87; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 0,0</t>
+          <t>-4,86; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; -0,26</t>
+          <t>-2,61; -0,26</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,55</t>
+          <t>0,0; 5,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,09</t>
+          <t>0,0; 4,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,62</t>
+          <t>0,31; 2,59</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,0</t>
+          <t>-3,39; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,0</t>
+          <t>-3,4; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,0</t>
+          <t>-2,4; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,0</t>
+          <t>-2,55; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,67</t>
+          <t>-1,69; 0,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,75</t>
+          <t>-1,14; 1,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,61</t>
+          <t>-0,66; 0,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,29</t>
+          <t>-0,37; 1,2</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,76</t>
+          <t>-1,56; 1,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 2,84</t>
+          <t>-1,25; 2,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,45</t>
+          <t>-2,22; 1,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,0</t>
+          <t>-3,34; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,29</t>
+          <t>-1,4; 1,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,75</t>
+          <t>-1,75; 0,82</t>
         </is>
       </c>
     </row>
@@ -1416,27 +1416,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,08</t>
+          <t>0,0; 5,07</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,23</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,11</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,08</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,46</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,73</t>
+          <t>-0,48; 0,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,39</t>
+          <t>-0,19; 1,26</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,51</t>
+          <t>-0,67; 0,59</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,33</t>
+          <t>-0,83; 0,27</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,42</t>
+          <t>-0,35; 0,51</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,6</t>
+          <t>-0,28; 0,59</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-80,13; 576,69</t>
+          <t>-80,55; 533,97</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-39,05; 995,23</t>
+          <t>-52,01; 910,26</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-85,56; 353,67</t>
+          <t>-81,99; 367,1</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 352,9</t>
+          <t>-100,0; 189,82</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-65,76; 167,31</t>
+          <t>-58,2; 223,84</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-53,15; 247,4</t>
+          <t>-46,0; 256,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1008-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1008-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,39</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-0,5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,5</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,39</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,39</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,0</t>
+          <t>-5,2; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,0</t>
+          <t>-4,88; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 0,0</t>
+          <t>-2,39; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 0,0</t>
+          <t>-2,06; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; -0,26</t>
+          <t>-2,63; -0,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; -0,26</t>
+          <t>-2,59; -0,26</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,64</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>1,56</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1,39</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,64</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,31</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 4,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,59</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,68</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,68</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,68</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,68</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,19; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,37; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,0</t>
+          <t>-2,18; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,0</t>
+          <t>-2,28; 0,0</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,46</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,69</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,73</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>-1,74; 0,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,33</t>
+          <t>-0,94; 1,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,59</t>
+          <t>-0,73; 0,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,2</t>
+          <t>-0,37; 1,3</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-50,89%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>67,42%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,09</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,28</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,53</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,09</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,86</t>
+          <t>-2,29; 1,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,76</t>
+          <t>-3,26; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,79</t>
+          <t>-1,5; 1,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,0</t>
+          <t>-1,25; 3,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,19</t>
+          <t>-1,32; 1,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,82</t>
+          <t>-1,75; 0,9</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-12,33%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>45,39%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>84,7%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-12,33%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1,73</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,94</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1,01</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,07</t>
+          <t>0,0; 4,71</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,75</t>
+          <t>0,0; 6,14</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,37</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
     </row>
@@ -1449,17 +1449,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,23</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,12</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>0,53</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,23</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,72</t>
+          <t>-0,72; 0,53</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,26</t>
+          <t>-0,83; 0,24</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,59</t>
+          <t>-0,4; 0,75</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,27</t>
+          <t>-0,17; 1,3</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,51</t>
+          <t>-0,39; 0,5</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,59</t>
+          <t>-0,31; 0,57</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-8,38%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-45,06%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>29,52%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>131,76%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-8,38%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-45,06%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-80,55; 533,97</t>
+          <t>-84,29; 311,74</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-52,01; 910,26</t>
+          <t>-100,0; 178,06</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-81,99; 367,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 189,82</t>
+          <t>-45,73; 927,08</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-58,2; 223,84</t>
+          <t>-59,02; 255,19</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-46,0; 256,64</t>
+          <t>-50,5; 235,08</t>
         </is>
       </c>
     </row>
